--- a/data/sars/alaska/tables/Alaska_2019_Appendix2.xlsx
+++ b/data/sars/alaska/tables/Alaska_2019_Appendix2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/evajuenglingbean/Desktop/Graduate Work/Marine Mammal Stock Assessment/2019/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4EBD2CAE-07E2-5744-8132-404C2DFE17E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED2C4C17-41C9-CD42-9BD1-BB6573590A87}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="780" windowWidth="34200" windowHeight="19780" xr2:uid="{57E25FEB-1DCC-DF4C-915A-99B6CF37F830}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="16980" windowHeight="21380" xr2:uid="{57E25FEB-1DCC-DF4C-915A-99B6CF37F830}"/>
   </bookViews>
   <sheets>
     <sheet name="tabula-Alaska_2019_Appendix2" sheetId="1" r:id="rId1"/>
@@ -29,9 +29,6 @@
     <t>NS</t>
   </si>
   <si>
-    <t>229a</t>
-  </si>
-  <si>
     <t>b</t>
   </si>
   <si>
@@ -224,7 +221,10 @@
     <t>last_survey</t>
   </si>
   <si>
-    <t>notes</t>
+    <t>comments</t>
+  </si>
+  <si>
+    <t>sim_native</t>
   </si>
 </sst>
 </file>
@@ -1108,54 +1108,58 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A1BC201C-695E-2C40-829A-80C8E4045123}">
-  <dimension ref="A1:L46"/>
+  <dimension ref="A1:M46"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="77.1640625" style="3" customWidth="1"/>
-    <col min="2" max="16384" width="10.83203125" style="3"/>
+    <col min="2" max="9" width="10.83203125" style="3"/>
+    <col min="11" max="16384" width="10.83203125" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="B1" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="C1" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="D1" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="E1" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="F1" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="G1" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="H1" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="I1" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="J1" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="K1" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="J1" s="3" t="s">
+      <c r="L1" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="K1" s="3" t="s">
+      <c r="M1" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="L1" s="3" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A2" s="3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B2" s="4">
         <v>53624</v>
@@ -1178,19 +1182,22 @@
       <c r="I2" s="3">
         <v>36</v>
       </c>
-      <c r="J2" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="K2" s="3">
+      <c r="J2">
+        <v>204</v>
+      </c>
+      <c r="K2" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="L2" s="3">
         <v>2018</v>
       </c>
-      <c r="L2" s="3" t="s">
+      <c r="M2" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A3" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B3" s="4">
         <v>43201</v>
@@ -1213,19 +1220,22 @@
       <c r="I3" s="3">
         <v>24</v>
       </c>
-      <c r="J3" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="K3" s="3">
+      <c r="J3">
+        <v>11</v>
+      </c>
+      <c r="K3" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="L3" s="3">
         <v>2017</v>
       </c>
-      <c r="L3" s="3" t="s">
+      <c r="M3" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A4" s="3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B4" s="4">
         <v>620660</v>
@@ -1251,16 +1261,19 @@
       <c r="I4" s="3">
         <v>2.2000000000000002</v>
       </c>
-      <c r="J4" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="K4" s="3">
+      <c r="J4">
+        <v>387</v>
+      </c>
+      <c r="K4" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="L4" s="3">
         <v>2016</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A5" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B5" s="4">
         <v>5588</v>
@@ -1283,19 +1296,22 @@
       <c r="I5" s="3">
         <v>0.4</v>
       </c>
-      <c r="J5" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="K5" s="3">
+      <c r="J5">
+        <v>90</v>
+      </c>
+      <c r="K5" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="L5" s="3">
         <v>2018</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A6" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>2</v>
+        <v>9</v>
+      </c>
+      <c r="B6" s="3">
+        <v>229</v>
       </c>
       <c r="D6" s="3">
         <v>229</v>
@@ -1315,19 +1331,22 @@
       <c r="I6" s="3">
         <v>0</v>
       </c>
-      <c r="J6" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="K6" s="3">
+      <c r="J6">
+        <v>0</v>
+      </c>
+      <c r="K6" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="L6" s="3">
         <v>2018</v>
       </c>
-      <c r="L6" s="3" t="s">
+      <c r="M6" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A7" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B7" s="4">
         <v>44781</v>
@@ -1350,16 +1369,19 @@
       <c r="I7" s="3">
         <v>3.8</v>
       </c>
-      <c r="J7" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="K7" s="3">
+      <c r="J7">
+        <v>15</v>
+      </c>
+      <c r="K7" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="L7" s="3">
         <v>2017</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A8" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B8" s="4">
         <v>8677</v>
@@ -1382,16 +1404,19 @@
       <c r="I8" s="3">
         <v>0.3</v>
       </c>
-      <c r="J8" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="K8" s="3">
+      <c r="J8">
+        <v>37</v>
+      </c>
+      <c r="K8" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="L8" s="3">
         <v>2017</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A9" s="3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B9" s="4">
         <v>26448</v>
@@ -1414,16 +1439,19 @@
       <c r="I9" s="3">
         <v>1.2</v>
       </c>
-      <c r="J9" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="K9" s="3">
+      <c r="J9">
+        <v>126</v>
+      </c>
+      <c r="K9" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="L9" s="3">
         <v>2017</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A10" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B10" s="4">
         <v>44756</v>
@@ -1446,16 +1474,19 @@
       <c r="I10" s="3">
         <v>24</v>
       </c>
-      <c r="J10" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="K10" s="3">
+      <c r="J10">
+        <v>387</v>
+      </c>
+      <c r="K10" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="L10" s="3">
         <v>2015</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A11" s="3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B11" s="4">
         <v>28411</v>
@@ -1478,16 +1509,19 @@
       <c r="I11" s="3">
         <v>2.5</v>
       </c>
-      <c r="J11" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="K11" s="3">
+      <c r="J11">
+        <v>104</v>
+      </c>
+      <c r="K11" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="L11" s="3">
         <v>2018</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A12" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B12" s="4">
         <v>7455</v>
@@ -1510,16 +1544,19 @@
       <c r="I12" s="3">
         <v>0</v>
       </c>
-      <c r="J12" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="K12" s="3">
+      <c r="J12">
+        <v>104</v>
+      </c>
+      <c r="K12" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="L12" s="3">
         <v>2017</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A13" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B13" s="4">
         <v>13388</v>
@@ -1542,16 +1579,19 @@
       <c r="I13" s="3">
         <v>0</v>
       </c>
-      <c r="J13" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="K13" s="3">
+      <c r="J13">
+        <v>50</v>
+      </c>
+      <c r="K13" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="L13" s="3">
         <v>2016</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A14" s="3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B14" s="4">
         <v>13289</v>
@@ -1574,16 +1614,19 @@
       <c r="I14" s="3">
         <v>0</v>
       </c>
-      <c r="J14" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="K14" s="3">
+      <c r="J14">
+        <v>77</v>
+      </c>
+      <c r="K14" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="L14" s="3">
         <v>2015</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A15" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B15" s="4">
         <v>23478</v>
@@ -1606,16 +1649,19 @@
       <c r="I15" s="3">
         <v>0</v>
       </c>
-      <c r="J15" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="K15" s="3">
+      <c r="J15">
+        <v>69</v>
+      </c>
+      <c r="K15" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="L15" s="3">
         <v>2015</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A16" s="3" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B16" s="4">
         <v>27659</v>
@@ -1638,16 +1684,19 @@
       <c r="I16" s="3">
         <v>0</v>
       </c>
-      <c r="J16" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="K16" s="3">
+      <c r="J16">
+        <v>40</v>
+      </c>
+      <c r="K16" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="L16" s="3">
         <v>2015</v>
       </c>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A17" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B17" s="4">
         <v>461625</v>
@@ -1670,16 +1719,19 @@
       <c r="I17" s="3">
         <v>0.9</v>
       </c>
-      <c r="J17" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="K17" s="3">
+      <c r="J17">
+        <v>328</v>
+      </c>
+      <c r="K17" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="L17" s="3">
         <v>2013</v>
       </c>
     </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A18" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E18" s="3">
         <v>0.12</v>
@@ -1693,19 +1745,22 @@
       <c r="I18" s="3">
         <v>1.6</v>
       </c>
-      <c r="J18" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="K18" s="3">
+      <c r="J18">
+        <v>549</v>
+      </c>
+      <c r="K18" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="L18" s="3">
         <v>2013</v>
       </c>
-      <c r="L18" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M18" s="2" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A19" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E19" s="3">
         <v>0.12</v>
@@ -1719,19 +1774,22 @@
       <c r="I19" s="3">
         <v>2.4</v>
       </c>
-      <c r="J19" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="K19" s="3">
+      <c r="J19">
+        <v>697</v>
+      </c>
+      <c r="K19" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="L19" s="3">
         <v>2013</v>
       </c>
-      <c r="L19" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M19" s="2" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A20" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B20" s="4">
         <v>184697</v>
@@ -1754,16 +1812,19 @@
       <c r="I20" s="3">
         <v>1.1000000000000001</v>
       </c>
-      <c r="J20" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="K20" s="3">
+      <c r="J20">
+        <v>2.8</v>
+      </c>
+      <c r="K20" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="L20" s="3">
         <v>2013</v>
       </c>
     </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A21" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B21" s="4">
         <v>39258</v>
@@ -1772,7 +1833,7 @@
         <v>0.22900000000000001</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E21" s="3">
         <v>0.04</v>
@@ -1781,7 +1842,7 @@
         <v>1</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H21" s="3">
         <v>139</v>
@@ -1789,16 +1850,19 @@
       <c r="I21" s="3">
         <v>0</v>
       </c>
-      <c r="J21" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="K21" s="3">
+      <c r="J21">
+        <v>139</v>
+      </c>
+      <c r="K21" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="L21" s="3">
         <v>1992</v>
       </c>
     </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A22" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B22" s="4">
         <v>20752</v>
@@ -1824,16 +1888,19 @@
       <c r="I22" s="3">
         <v>0.2</v>
       </c>
-      <c r="J22" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="K22" s="3">
+      <c r="J22">
+        <v>67</v>
+      </c>
+      <c r="K22" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="L22" s="3">
         <v>2012</v>
       </c>
     </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A23" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B23" s="4">
         <v>6994</v>
@@ -1842,7 +1909,7 @@
         <v>0.37</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E23" s="3">
         <v>0.04</v>
@@ -1851,7 +1918,7 @@
         <v>1</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H23" s="3">
         <v>206</v>
@@ -1859,16 +1926,19 @@
       <c r="I23" s="3">
         <v>0.2</v>
       </c>
-      <c r="J23" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="K23" s="3">
+      <c r="J23">
+        <v>206</v>
+      </c>
+      <c r="K23" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="L23" s="3">
         <v>2000</v>
       </c>
     </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A24" s="3" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B24" s="4">
         <v>1926</v>
@@ -1877,7 +1947,7 @@
         <v>0.25</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E24" s="3">
         <v>4.8000000000000001E-2</v>
@@ -1886,7 +1956,7 @@
         <v>1</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H24" s="3">
         <v>25</v>
@@ -1894,16 +1964,19 @@
       <c r="I24" s="3">
         <v>0.2</v>
       </c>
-      <c r="J24" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="K24" s="3">
+      <c r="J24">
+        <v>25</v>
+      </c>
+      <c r="K24" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="L24" s="3">
         <v>2005</v>
       </c>
     </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A25" s="3" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B25" s="3">
         <v>327</v>
@@ -1926,25 +1999,28 @@
       <c r="I25" s="3">
         <v>0</v>
       </c>
-      <c r="J25" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="K25" s="3">
+      <c r="J25">
+        <v>0</v>
+      </c>
+      <c r="K25" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="L25" s="3">
         <v>2016</v>
       </c>
-      <c r="L25" s="3" t="s">
+      <c r="M25" s="2" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="26" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A26" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="B26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A26" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="B26" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="D26" s="3" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E26" s="3">
         <v>0.04</v>
@@ -1953,7 +2029,7 @@
         <v>0.5</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H26" s="3">
         <v>0</v>
@@ -1961,19 +2037,22 @@
       <c r="I26" s="3">
         <v>0</v>
       </c>
-      <c r="J26" s="3" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="J26">
+        <v>0</v>
+      </c>
+      <c r="K26" s="3" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A27" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B27" s="4">
         <v>2347</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D27" s="4">
         <v>2347</v>
@@ -1993,25 +2072,28 @@
       <c r="I27" s="3">
         <v>1</v>
       </c>
-      <c r="J27" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="K27" s="3">
+      <c r="J27">
+        <v>0</v>
+      </c>
+      <c r="K27" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="L27" s="3">
         <v>2012</v>
       </c>
-      <c r="L27" s="3" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M27" s="2" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="28" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A28" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B28" s="3">
         <v>302</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D28" s="3">
         <v>302</v>
@@ -2031,25 +2113,28 @@
       <c r="I28" s="3">
         <v>0</v>
       </c>
-      <c r="J28" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="K28" s="3">
+      <c r="J28">
+        <v>0</v>
+      </c>
+      <c r="K28" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="L28" s="3">
         <v>2018</v>
       </c>
-      <c r="L28" s="3" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M28" s="2" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="29" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A29" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B29" s="3">
         <v>587</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D29" s="3">
         <v>587</v>
@@ -2069,25 +2154,28 @@
       <c r="I29" s="3">
         <v>1</v>
       </c>
-      <c r="J29" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="K29" s="3">
+      <c r="J29">
+        <v>0</v>
+      </c>
+      <c r="K29" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="L29" s="3">
         <v>2012</v>
       </c>
-      <c r="L29" s="3" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M29" s="2" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="30" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A30" s="3" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B30" s="3">
         <v>7</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D30" s="3">
         <v>7</v>
@@ -2107,25 +2195,28 @@
       <c r="I30" s="3">
         <v>0</v>
       </c>
-      <c r="J30" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="K30" s="3">
+      <c r="J30">
+        <v>0</v>
+      </c>
+      <c r="K30" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="L30" s="3">
         <v>2018</v>
       </c>
-      <c r="L30" s="3" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M30" s="2" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="31" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A31" s="3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B31" s="3">
         <v>243</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D31" s="3">
         <v>243</v>
@@ -2145,28 +2236,31 @@
       <c r="I31" s="3">
         <v>0</v>
       </c>
-      <c r="J31" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="K31" s="3">
+      <c r="J31">
+        <v>0</v>
+      </c>
+      <c r="K31" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="L31" s="3">
         <v>2009</v>
       </c>
-      <c r="L31" s="3" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M31" s="2" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="32" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A32" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B32" s="4">
         <v>26880</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E32" s="3">
         <v>0.04</v>
@@ -2175,7 +2269,7 @@
         <v>0.5</v>
       </c>
       <c r="G32" s="3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H32" s="3">
         <v>0</v>
@@ -2183,16 +2277,19 @@
       <c r="I32" s="3">
         <v>0</v>
       </c>
-      <c r="J32" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="K32" s="3">
+      <c r="J32">
+        <v>0</v>
+      </c>
+      <c r="K32" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="L32" s="3">
         <v>1990</v>
       </c>
     </row>
-    <row r="33" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A33" s="3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E33" s="3">
         <v>0.04</v>
@@ -2206,19 +2303,22 @@
       <c r="I33" s="3">
         <v>34</v>
       </c>
-      <c r="J33" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="K33" s="3">
+      <c r="J33">
+        <v>0</v>
+      </c>
+      <c r="K33" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="L33" s="3">
         <v>2012</v>
       </c>
-      <c r="L33" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="34" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M33" s="2" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="34" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A34" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B34" s="4">
         <v>31046</v>
@@ -2227,7 +2327,7 @@
         <v>0.21</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E34" s="3">
         <v>0.04</v>
@@ -2236,7 +2336,7 @@
         <v>0.5</v>
       </c>
       <c r="G34" s="3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H34" s="3">
         <v>72</v>
@@ -2244,16 +2344,19 @@
       <c r="I34" s="3">
         <v>72</v>
       </c>
-      <c r="J34" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="K34" s="3">
+      <c r="J34">
+        <v>0</v>
+      </c>
+      <c r="K34" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="L34" s="3">
         <v>1998</v>
       </c>
     </row>
-    <row r="35" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A35" s="3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B35" s="4">
         <v>48215</v>
@@ -2262,7 +2365,7 @@
         <v>0.22</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E35" s="3">
         <v>0.04</v>
@@ -2271,7 +2374,7 @@
         <v>0.5</v>
       </c>
       <c r="G35" s="3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H35" s="3">
         <v>0.2</v>
@@ -2279,16 +2382,19 @@
       <c r="I35" s="3">
         <v>0.2</v>
       </c>
-      <c r="J35" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="K35" s="3">
+      <c r="J35">
+        <v>0</v>
+      </c>
+      <c r="K35" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="L35" s="3">
         <v>1999</v>
       </c>
     </row>
-    <row r="36" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A36" s="3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B36" s="4">
         <v>83400</v>
@@ -2297,7 +2403,7 @@
         <v>9.7000000000000003E-2</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E36" s="3">
         <v>0.04</v>
@@ -2306,7 +2412,7 @@
         <v>1</v>
       </c>
       <c r="G36" s="3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H36" s="3">
         <v>38</v>
@@ -2314,16 +2420,19 @@
       <c r="I36" s="3">
         <v>38</v>
       </c>
-      <c r="J36" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="K36" s="3">
+      <c r="J36">
+        <v>0</v>
+      </c>
+      <c r="K36" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="L36" s="3">
         <v>1991</v>
       </c>
     </row>
-    <row r="37" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A37" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E37" s="3">
         <v>0.04</v>
@@ -2337,25 +2446,28 @@
       <c r="I37" s="3">
         <v>4.7</v>
       </c>
-      <c r="J37" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="K37" s="3">
+      <c r="J37">
+        <v>0</v>
+      </c>
+      <c r="K37" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="L37" s="3">
         <v>2015</v>
       </c>
-      <c r="L37" s="3" t="s">
+      <c r="M37" s="2" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="38" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A38" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B38" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="38" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A38" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B38" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="D38" s="3" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E38" s="3">
         <v>0.04</v>
@@ -2364,7 +2476,7 @@
         <v>0.5</v>
       </c>
       <c r="G38" s="3" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H38" s="3">
         <v>0</v>
@@ -2372,19 +2484,22 @@
       <c r="I38" s="3">
         <v>0</v>
       </c>
-      <c r="J38" s="3" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="39" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="J38">
+        <v>0</v>
+      </c>
+      <c r="K38" s="3" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A39" s="3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E39" s="3">
         <v>0.04</v>
@@ -2393,7 +2508,7 @@
         <v>0.5</v>
       </c>
       <c r="G39" s="3" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H39" s="3">
         <v>0</v>
@@ -2401,19 +2516,22 @@
       <c r="I39" s="3">
         <v>0</v>
       </c>
-      <c r="J39" s="3" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="40" spans="1:12" ht="17" x14ac:dyDescent="0.2">
+      <c r="J39">
+        <v>0</v>
+      </c>
+      <c r="K39" s="3" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40" spans="1:13" ht="17" x14ac:dyDescent="0.2">
       <c r="A40" s="5" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E40" s="3">
         <v>0.04</v>
@@ -2422,7 +2540,7 @@
         <v>0.5</v>
       </c>
       <c r="G40" s="3" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H40" s="3">
         <v>0</v>
@@ -2430,13 +2548,16 @@
       <c r="I40" s="3">
         <v>0</v>
       </c>
-      <c r="J40" s="3" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="41" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="J40">
+        <v>0</v>
+      </c>
+      <c r="K40" s="3" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A41" s="3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B41" s="4">
         <v>1107</v>
@@ -2462,16 +2583,19 @@
       <c r="I41" s="3">
         <v>0.7</v>
       </c>
-      <c r="J41" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="K41" s="3">
+      <c r="J41">
+        <v>0</v>
+      </c>
+      <c r="K41" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="L41" s="3">
         <v>2006</v>
       </c>
     </row>
-    <row r="42" spans="1:12" ht="17" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:13" ht="17" x14ac:dyDescent="0.2">
       <c r="A42" s="5" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B42" s="4">
         <v>10103</v>
@@ -2497,16 +2621,19 @@
       <c r="I42" s="3">
         <v>9.5</v>
       </c>
-      <c r="J42" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="K42" s="3">
+      <c r="J42">
+        <v>0</v>
+      </c>
+      <c r="K42" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="L42" s="3">
         <v>2006</v>
       </c>
     </row>
-    <row r="43" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A43" s="3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E43" s="3">
         <v>0.04</v>
@@ -2520,25 +2647,28 @@
       <c r="I43" s="3">
         <v>0</v>
       </c>
-      <c r="J43" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="K43" s="3">
+      <c r="J43">
+        <v>0</v>
+      </c>
+      <c r="K43" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="L43" s="3">
         <v>2013</v>
       </c>
-      <c r="L43" s="3" t="s">
+      <c r="M43" s="2" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="44" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A44" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="B44" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A44" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="B44" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="D44" s="3" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E44" s="3">
         <v>0.04</v>
@@ -2547,7 +2677,7 @@
         <v>0.5</v>
       </c>
       <c r="G44" s="3" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H44" s="3">
         <v>0</v>
@@ -2555,13 +2685,16 @@
       <c r="I44" s="3">
         <v>0</v>
       </c>
-      <c r="J44" s="3" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="45" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="J44">
+        <v>0</v>
+      </c>
+      <c r="K44" s="3" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A45" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B45" s="3">
         <v>31</v>
@@ -2584,19 +2717,22 @@
       <c r="I45" s="3">
         <v>0</v>
       </c>
-      <c r="J45" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="K45" s="3">
+      <c r="J45">
+        <v>0</v>
+      </c>
+      <c r="K45" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="L45" s="3">
         <v>2015</v>
       </c>
-      <c r="L45" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="46" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M45" s="2" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="46" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A46" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B46" s="4">
         <v>16820</v>
@@ -2622,10 +2758,13 @@
       <c r="I46" s="3">
         <v>0.2</v>
       </c>
-      <c r="J46" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="K46" s="3">
+      <c r="J46">
+        <v>53</v>
+      </c>
+      <c r="K46" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="L46" s="3">
         <v>2011</v>
       </c>
     </row>
@@ -2644,26 +2783,26 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B1" t="s">
         <v>51</v>
-      </c>
-      <c r="B1" t="s">
-        <v>52</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.2">
